--- a/version_1_photo_with_camera/vision_llm_output/receipts.xlsx
+++ b/version_1_photo_with_camera/vision_llm_output/receipts.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,28 +495,145 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-27T12:51:14</t>
+          <t>2026-09-28T21:04:15</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Generated_invoice</t>
+          <t>Generated_po</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>บจก. ไอ-บรีซ (สำนักงานใหญ่)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0105555555555</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>สั่งซื้อคอร์สเรียน TOEIC 1 สิทธิ์ x1 = 2500.0</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>2500</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2500</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>THB</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-27T12:55:55</t>
+          <t>2026-09-28T21:07:22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Generated_quotation</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ร้านซีฟู้ดหาดใหญ่</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>ปลากะพง, กุ้งแม่น้ำ x15 = 2250.0</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>2250</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2250</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-28T21:08:51</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>Generated_invoice</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ร้านสุกี้ฟ้าผ่าแห้ง</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>บริการจัดการคอนเทนต์ และ ค่าถ่ายวิดีโอ x1 = 5000.0</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L4" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09-28T21:09:58</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Generated_tax_invoice</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>บริษัท คลิกเน็กซ์ จำกัด</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0105551234567</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>ระบบ x1 = 15000.0</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>15000</v>
+      </c>
+      <c r="L5" t="n">
+        <v>15000</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/version_1_photo_with_camera/vision_llm_output/receipts.xlsx
+++ b/version_1_photo_with_camera/vision_llm_output/receipts.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -633,7 +633,66 @@
           <t>THB</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-16T19:10:37</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>636395911945912644.jpg</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>บริษัทส่งเสริมการค้าคุณสมบัติ</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>INV-202609282108</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0822222222</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>ผู้หญิงที่สั่งซื้อผ้าผิวสีน้ำตาล x1 = 3500.0; ผู้หญิงที่สั่งซื้อผ้าผิวสีส้ม x1 = 5000.0</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>3500</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>5350</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
